--- a/BWI/bestwine_output/bestwine_Bulgaria.xlsx
+++ b/BWI/bestwine_output/bestwine_Bulgaria.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA190"/>
+  <dimension ref="A1:AA192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -20211,6 +20211,240 @@
       <c r="Z190" s="2" t="inlineStr"/>
       <c r="AA190" s="2" t="inlineStr"/>
     </row>
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t>Antastico Group Ood</t>
+        </is>
+      </c>
+      <c r="B191" s="2" t="inlineStr">
+        <is>
+          <t>Antastico Group Ood</t>
+        </is>
+      </c>
+      <c r="C191" s="2" t="inlineStr">
+        <is>
+          <t>34077</t>
+        </is>
+      </c>
+      <c r="D191" s="2" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="E191" s="2" t="inlineStr">
+        <is>
+          <t>Simeonovo</t>
+        </is>
+      </c>
+      <c r="F191" s="2" t="inlineStr">
+        <is>
+          <t>Sofia</t>
+        </is>
+      </c>
+      <c r="G191" s="2" t="inlineStr">
+        <is>
+          <t>Ul. Momina Salsa No.14a</t>
+        </is>
+      </c>
+      <c r="H191" s="2" t="inlineStr">
+        <is>
+          <t>1434</t>
+        </is>
+      </c>
+      <c r="I191" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fantastico.bg</t>
+        </is>
+      </c>
+      <c r="J191" s="2" t="inlineStr"/>
+      <c r="K191" s="2" t="inlineStr"/>
+      <c r="L191" s="2" t="inlineStr">
+        <is>
+          <t>3479</t>
+        </is>
+      </c>
+      <c r="M191" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N191" s="2" t="inlineStr">
+        <is>
+          <t>denica.dimitrova@fantastico.bg</t>
+        </is>
+      </c>
+      <c r="O191" s="2" t="inlineStr">
+        <is>
+          <t>+359 2 969 2500</t>
+        </is>
+      </c>
+      <c r="P191" s="2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="Q191" s="2" t="inlineStr">
+        <is>
+          <t>206255903</t>
+        </is>
+      </c>
+      <c r="R191" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/chain-stores-fantastico/</t>
+        </is>
+      </c>
+      <c r="S191" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/fantastico.stores/</t>
+        </is>
+      </c>
+      <c r="T191" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/fantasticostores</t>
+        </is>
+      </c>
+      <c r="U191" s="2" t="inlineStr"/>
+      <c r="V191" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCu7ZlcAyDfZ8QcGcP-9FVtw</t>
+        </is>
+      </c>
+      <c r="W191" s="2" t="inlineStr">
+        <is>
+          <t>Adrian Tsonev</t>
+        </is>
+      </c>
+      <c r="X191" s="2" t="inlineStr">
+        <is>
+          <t>Commercial Director</t>
+        </is>
+      </c>
+      <c r="Y191" s="2" t="inlineStr"/>
+      <c r="Z191" s="2" t="inlineStr"/>
+      <c r="AA191" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/adrian-tsonev-5020ab170/</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
+        <is>
+          <t>Antastico Group Ood</t>
+        </is>
+      </c>
+      <c r="B192" s="2" t="inlineStr">
+        <is>
+          <t>Antastico Group Ood</t>
+        </is>
+      </c>
+      <c r="C192" s="2" t="inlineStr">
+        <is>
+          <t>34077</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="E192" s="2" t="inlineStr">
+        <is>
+          <t>Simeonovo</t>
+        </is>
+      </c>
+      <c r="F192" s="2" t="inlineStr">
+        <is>
+          <t>Sofia</t>
+        </is>
+      </c>
+      <c r="G192" s="2" t="inlineStr">
+        <is>
+          <t>Ul. Momina Salsa No.14a</t>
+        </is>
+      </c>
+      <c r="H192" s="2" t="inlineStr">
+        <is>
+          <t>1434</t>
+        </is>
+      </c>
+      <c r="I192" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fantastico.bg</t>
+        </is>
+      </c>
+      <c r="J192" s="2" t="inlineStr"/>
+      <c r="K192" s="2" t="inlineStr"/>
+      <c r="L192" s="2" t="inlineStr">
+        <is>
+          <t>3479</t>
+        </is>
+      </c>
+      <c r="M192" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N192" s="2" t="inlineStr">
+        <is>
+          <t>denica.dimitrova@fantastico.bg</t>
+        </is>
+      </c>
+      <c r="O192" s="2" t="inlineStr">
+        <is>
+          <t>+359 2 969 2500</t>
+        </is>
+      </c>
+      <c r="P192" s="2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="Q192" s="2" t="inlineStr">
+        <is>
+          <t>206255903</t>
+        </is>
+      </c>
+      <c r="R192" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/chain-stores-fantastico/</t>
+        </is>
+      </c>
+      <c r="S192" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/fantastico.stores/</t>
+        </is>
+      </c>
+      <c r="T192" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/fantasticostores</t>
+        </is>
+      </c>
+      <c r="U192" s="2" t="inlineStr"/>
+      <c r="V192" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCu7ZlcAyDfZ8QcGcP-9FVtw</t>
+        </is>
+      </c>
+      <c r="W192" s="2" t="inlineStr">
+        <is>
+          <t>Denica Dimitrova</t>
+        </is>
+      </c>
+      <c r="X192" s="2" t="inlineStr">
+        <is>
+          <t>Buyer</t>
+        </is>
+      </c>
+      <c r="Y192" s="2" t="inlineStr"/>
+      <c r="Z192" s="2" t="inlineStr"/>
+      <c r="AA192" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/denica-dimitrova-85a264113/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Bulgaria.xlsx
+++ b/BWI/bestwine_output/bestwine_Bulgaria.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA192"/>
+  <dimension ref="A1:AA195"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -20445,6 +20445,333 @@
         </is>
       </c>
     </row>
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr">
+        <is>
+          <t>Avinissima Wine and Food Consulting</t>
+        </is>
+      </c>
+      <c r="B193" s="2" t="inlineStr"/>
+      <c r="C193" s="2" t="inlineStr">
+        <is>
+          <t>167433</t>
+        </is>
+      </c>
+      <c r="D193" s="2" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="E193" s="2" t="inlineStr">
+        <is>
+          <t>Sofia</t>
+        </is>
+      </c>
+      <c r="F193" s="2" t="inlineStr">
+        <is>
+          <t>Sofia</t>
+        </is>
+      </c>
+      <c r="G193" s="2" t="inlineStr">
+        <is>
+          <t>11 Budapest Street</t>
+        </is>
+      </c>
+      <c r="H193" s="2" t="inlineStr"/>
+      <c r="I193" s="2" t="inlineStr">
+        <is>
+          <t>https://www.vinoto.com</t>
+        </is>
+      </c>
+      <c r="J193" s="2" t="inlineStr"/>
+      <c r="K193" s="2" t="inlineStr"/>
+      <c r="L193" s="2" t="inlineStr"/>
+      <c r="M193" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N193" s="2" t="inlineStr">
+        <is>
+          <t>hello@vinoto.com</t>
+        </is>
+      </c>
+      <c r="O193" s="2" t="inlineStr"/>
+      <c r="P193" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q193" s="2" t="inlineStr"/>
+      <c r="R193" s="2" t="inlineStr"/>
+      <c r="S193" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/vinotocom/</t>
+        </is>
+      </c>
+      <c r="T193" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/vinoto_com/</t>
+        </is>
+      </c>
+      <c r="U193" s="2" t="inlineStr"/>
+      <c r="V193" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/channel/UCeSAZblYJpIZ6Bp_yRKTlcQ</t>
+        </is>
+      </c>
+      <c r="W193" s="2" t="inlineStr">
+        <is>
+          <t>Irina Sofranova</t>
+        </is>
+      </c>
+      <c r="X193" s="2" t="inlineStr">
+        <is>
+          <t>Manager and Co-owner</t>
+        </is>
+      </c>
+      <c r="Y193" s="2" t="inlineStr"/>
+      <c r="Z193" s="2" t="inlineStr"/>
+      <c r="AA193" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/irina-sofranova-5505131/</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
+        <is>
+          <t>Antastico Group Ood</t>
+        </is>
+      </c>
+      <c r="B194" s="2" t="inlineStr">
+        <is>
+          <t>Antastico Group Ood</t>
+        </is>
+      </c>
+      <c r="C194" s="2" t="inlineStr">
+        <is>
+          <t>34077</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="E194" s="2" t="inlineStr">
+        <is>
+          <t>Simeonovo</t>
+        </is>
+      </c>
+      <c r="F194" s="2" t="inlineStr">
+        <is>
+          <t>Sofia</t>
+        </is>
+      </c>
+      <c r="G194" s="2" t="inlineStr">
+        <is>
+          <t>Ul. Momina Salsa No.14a</t>
+        </is>
+      </c>
+      <c r="H194" s="2" t="inlineStr">
+        <is>
+          <t>1434</t>
+        </is>
+      </c>
+      <c r="I194" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fantastico.bg</t>
+        </is>
+      </c>
+      <c r="J194" s="2" t="inlineStr"/>
+      <c r="K194" s="2" t="inlineStr"/>
+      <c r="L194" s="2" t="inlineStr">
+        <is>
+          <t>3479</t>
+        </is>
+      </c>
+      <c r="M194" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N194" s="2" t="inlineStr">
+        <is>
+          <t>denica.dimitrova@fantastico.bg</t>
+        </is>
+      </c>
+      <c r="O194" s="2" t="inlineStr">
+        <is>
+          <t>+359 2 969 2500</t>
+        </is>
+      </c>
+      <c r="P194" s="2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="Q194" s="2" t="inlineStr">
+        <is>
+          <t>206255903</t>
+        </is>
+      </c>
+      <c r="R194" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/chain-stores-fantastico/</t>
+        </is>
+      </c>
+      <c r="S194" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/fantastico.stores/</t>
+        </is>
+      </c>
+      <c r="T194" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/fantasticostores</t>
+        </is>
+      </c>
+      <c r="U194" s="2" t="inlineStr"/>
+      <c r="V194" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCu7ZlcAyDfZ8QcGcP-9FVtw</t>
+        </is>
+      </c>
+      <c r="W194" s="2" t="inlineStr">
+        <is>
+          <t>Adrian Tsonev</t>
+        </is>
+      </c>
+      <c r="X194" s="2" t="inlineStr">
+        <is>
+          <t>Commercial Director</t>
+        </is>
+      </c>
+      <c r="Y194" s="2" t="inlineStr"/>
+      <c r="Z194" s="2" t="inlineStr"/>
+      <c r="AA194" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/adrian-tsonev-5020ab170/</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr">
+        <is>
+          <t>Antastico Group Ood</t>
+        </is>
+      </c>
+      <c r="B195" s="2" t="inlineStr">
+        <is>
+          <t>Antastico Group Ood</t>
+        </is>
+      </c>
+      <c r="C195" s="2" t="inlineStr">
+        <is>
+          <t>34077</t>
+        </is>
+      </c>
+      <c r="D195" s="2" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="E195" s="2" t="inlineStr">
+        <is>
+          <t>Simeonovo</t>
+        </is>
+      </c>
+      <c r="F195" s="2" t="inlineStr">
+        <is>
+          <t>Sofia</t>
+        </is>
+      </c>
+      <c r="G195" s="2" t="inlineStr">
+        <is>
+          <t>Ul. Momina Salsa No.14a</t>
+        </is>
+      </c>
+      <c r="H195" s="2" t="inlineStr">
+        <is>
+          <t>1434</t>
+        </is>
+      </c>
+      <c r="I195" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fantastico.bg</t>
+        </is>
+      </c>
+      <c r="J195" s="2" t="inlineStr"/>
+      <c r="K195" s="2" t="inlineStr"/>
+      <c r="L195" s="2" t="inlineStr">
+        <is>
+          <t>3479</t>
+        </is>
+      </c>
+      <c r="M195" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N195" s="2" t="inlineStr">
+        <is>
+          <t>denica.dimitrova@fantastico.bg</t>
+        </is>
+      </c>
+      <c r="O195" s="2" t="inlineStr">
+        <is>
+          <t>+359 2 969 2500</t>
+        </is>
+      </c>
+      <c r="P195" s="2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="Q195" s="2" t="inlineStr">
+        <is>
+          <t>206255903</t>
+        </is>
+      </c>
+      <c r="R195" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/chain-stores-fantastico/</t>
+        </is>
+      </c>
+      <c r="S195" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/fantastico.stores/</t>
+        </is>
+      </c>
+      <c r="T195" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/fantasticostores</t>
+        </is>
+      </c>
+      <c r="U195" s="2" t="inlineStr"/>
+      <c r="V195" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCu7ZlcAyDfZ8QcGcP-9FVtw</t>
+        </is>
+      </c>
+      <c r="W195" s="2" t="inlineStr">
+        <is>
+          <t>Denica Dimitrova</t>
+        </is>
+      </c>
+      <c r="X195" s="2" t="inlineStr">
+        <is>
+          <t>Buyer</t>
+        </is>
+      </c>
+      <c r="Y195" s="2" t="inlineStr"/>
+      <c r="Z195" s="2" t="inlineStr"/>
+      <c r="AA195" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/denica-dimitrova-85a264113/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Bulgaria.xlsx
+++ b/BWI/bestwine_output/bestwine_Bulgaria.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA195"/>
+  <dimension ref="A1:AA202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -20772,6 +20772,729 @@
         </is>
       </c>
     </row>
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr">
+        <is>
+          <t>Best Wine Ltd.</t>
+        </is>
+      </c>
+      <c r="B196" s="2" t="inlineStr">
+        <is>
+          <t>Best Wine Ltd.</t>
+        </is>
+      </c>
+      <c r="C196" s="2" t="inlineStr">
+        <is>
+          <t>2207</t>
+        </is>
+      </c>
+      <c r="D196" s="2" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="E196" s="2" t="inlineStr">
+        <is>
+          <t>Sofia</t>
+        </is>
+      </c>
+      <c r="F196" s="2" t="inlineStr">
+        <is>
+          <t>Sofia-City</t>
+        </is>
+      </c>
+      <c r="G196" s="2" t="inlineStr">
+        <is>
+          <t>11 Ulitsa Andrey Germanov</t>
+        </is>
+      </c>
+      <c r="H196" s="2" t="inlineStr">
+        <is>
+          <t>1360</t>
+        </is>
+      </c>
+      <c r="I196" s="2" t="inlineStr">
+        <is>
+          <t>https://bestwine.bg</t>
+        </is>
+      </c>
+      <c r="J196" s="2" t="inlineStr"/>
+      <c r="K196" s="2" t="inlineStr"/>
+      <c r="L196" s="2" t="inlineStr"/>
+      <c r="M196" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N196" s="2" t="inlineStr">
+        <is>
+          <t>office@bestwine.bg</t>
+        </is>
+      </c>
+      <c r="O196" s="2" t="inlineStr"/>
+      <c r="P196" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q196" s="2" t="inlineStr"/>
+      <c r="R196" s="2" t="inlineStr"/>
+      <c r="S196" s="2" t="inlineStr"/>
+      <c r="T196" s="2" t="inlineStr"/>
+      <c r="U196" s="2" t="inlineStr"/>
+      <c r="V196" s="2" t="inlineStr"/>
+      <c r="W196" s="2" t="inlineStr">
+        <is>
+          <t>Dimitar (Hristov) Kuzmov</t>
+        </is>
+      </c>
+      <c r="X196" s="2" t="inlineStr">
+        <is>
+          <t>Sales And Marketing Manager</t>
+        </is>
+      </c>
+      <c r="Y196" s="2" t="inlineStr"/>
+      <c r="Z196" s="2" t="inlineStr"/>
+      <c r="AA196" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/dimitar-kuzmov-34a1538a/</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="inlineStr">
+        <is>
+          <t>Winebox Eood</t>
+        </is>
+      </c>
+      <c r="B197" s="2" t="inlineStr">
+        <is>
+          <t>Winebox Eood</t>
+        </is>
+      </c>
+      <c r="C197" s="2" t="inlineStr">
+        <is>
+          <t>2202</t>
+        </is>
+      </c>
+      <c r="D197" s="2" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="E197" s="2" t="inlineStr">
+        <is>
+          <t>Sofia</t>
+        </is>
+      </c>
+      <c r="F197" s="2" t="inlineStr">
+        <is>
+          <t>Sofia-City</t>
+        </is>
+      </c>
+      <c r="G197" s="2" t="inlineStr">
+        <is>
+          <t>33 Ulitsa Iskar</t>
+        </is>
+      </c>
+      <c r="H197" s="2" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="I197" s="2" t="inlineStr">
+        <is>
+          <t>https://www.winebox.bg</t>
+        </is>
+      </c>
+      <c r="J197" s="2" t="inlineStr"/>
+      <c r="K197" s="2" t="inlineStr"/>
+      <c r="L197" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M197" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N197" s="2" t="inlineStr">
+        <is>
+          <t>office@winebox.bg</t>
+        </is>
+      </c>
+      <c r="O197" s="2" t="inlineStr"/>
+      <c r="P197" s="2" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="Q197" s="2" t="inlineStr">
+        <is>
+          <t>175378641</t>
+        </is>
+      </c>
+      <c r="R197" s="2" t="inlineStr"/>
+      <c r="S197" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/WineboxLTD</t>
+        </is>
+      </c>
+      <c r="T197" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/winebox_ltd/</t>
+        </is>
+      </c>
+      <c r="U197" s="2" t="inlineStr"/>
+      <c r="V197" s="2" t="inlineStr"/>
+      <c r="W197" s="2" t="inlineStr">
+        <is>
+          <t>Svetla Karabadjakova</t>
+        </is>
+      </c>
+      <c r="X197" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y197" s="2" t="inlineStr"/>
+      <c r="Z197" s="2" t="inlineStr"/>
+      <c r="AA197" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/svetla-karabadjakova-0a160225</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t>Winebox Eood</t>
+        </is>
+      </c>
+      <c r="B198" s="2" t="inlineStr">
+        <is>
+          <t>Winebox Eood</t>
+        </is>
+      </c>
+      <c r="C198" s="2" t="inlineStr">
+        <is>
+          <t>2202</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="E198" s="2" t="inlineStr">
+        <is>
+          <t>Sofia</t>
+        </is>
+      </c>
+      <c r="F198" s="2" t="inlineStr">
+        <is>
+          <t>Sofia-City</t>
+        </is>
+      </c>
+      <c r="G198" s="2" t="inlineStr">
+        <is>
+          <t>33 Ulitsa Iskar</t>
+        </is>
+      </c>
+      <c r="H198" s="2" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="I198" s="2" t="inlineStr">
+        <is>
+          <t>https://www.winebox.bg</t>
+        </is>
+      </c>
+      <c r="J198" s="2" t="inlineStr"/>
+      <c r="K198" s="2" t="inlineStr"/>
+      <c r="L198" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M198" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N198" s="2" t="inlineStr">
+        <is>
+          <t>office@winebox.bg</t>
+        </is>
+      </c>
+      <c r="O198" s="2" t="inlineStr"/>
+      <c r="P198" s="2" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="Q198" s="2" t="inlineStr">
+        <is>
+          <t>175378641</t>
+        </is>
+      </c>
+      <c r="R198" s="2" t="inlineStr"/>
+      <c r="S198" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/WineboxLTD</t>
+        </is>
+      </c>
+      <c r="T198" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/winebox_ltd/</t>
+        </is>
+      </c>
+      <c r="U198" s="2" t="inlineStr"/>
+      <c r="V198" s="2" t="inlineStr"/>
+      <c r="W198" s="2" t="inlineStr">
+        <is>
+          <t>Nikolay Dalakov</t>
+        </is>
+      </c>
+      <c r="X198" s="2" t="inlineStr">
+        <is>
+          <t>General Manager</t>
+        </is>
+      </c>
+      <c r="Y198" s="2" t="inlineStr"/>
+      <c r="Z198" s="2" t="inlineStr"/>
+      <c r="AA198" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/nikolay-dalakov-7118188a/</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="inlineStr">
+        <is>
+          <t>Drinklink.bg</t>
+        </is>
+      </c>
+      <c r="B199" s="2" t="inlineStr">
+        <is>
+          <t>Drinklink.bg</t>
+        </is>
+      </c>
+      <c r="C199" s="2" t="inlineStr">
+        <is>
+          <t>31640</t>
+        </is>
+      </c>
+      <c r="D199" s="2" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="E199" s="2" t="inlineStr">
+        <is>
+          <t>Sofia</t>
+        </is>
+      </c>
+      <c r="F199" s="2" t="inlineStr">
+        <is>
+          <t>Sofia-City</t>
+        </is>
+      </c>
+      <c r="G199" s="2" t="inlineStr">
+        <is>
+          <t>22 Ulitsa</t>
+        </is>
+      </c>
+      <c r="H199" s="2" t="inlineStr">
+        <is>
+          <t>1138</t>
+        </is>
+      </c>
+      <c r="I199" s="2" t="inlineStr">
+        <is>
+          <t>https://drinklink.bg</t>
+        </is>
+      </c>
+      <c r="J199" s="2" t="inlineStr"/>
+      <c r="K199" s="2" t="inlineStr"/>
+      <c r="L199" s="2" t="inlineStr"/>
+      <c r="M199" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N199" s="2" t="inlineStr">
+        <is>
+          <t>info@drinklink.bg</t>
+        </is>
+      </c>
+      <c r="O199" s="2" t="inlineStr"/>
+      <c r="P199" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q199" s="2" t="inlineStr"/>
+      <c r="R199" s="2" t="inlineStr"/>
+      <c r="S199" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/DrinkLinkbg-100157172487583/</t>
+        </is>
+      </c>
+      <c r="T199" s="2" t="inlineStr"/>
+      <c r="U199" s="2" t="inlineStr"/>
+      <c r="V199" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@drinklinkbg</t>
+        </is>
+      </c>
+      <c r="W199" s="2" t="inlineStr">
+        <is>
+          <t>Pencho Dinev</t>
+        </is>
+      </c>
+      <c r="X199" s="2" t="inlineStr">
+        <is>
+          <t>Marketing And Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y199" s="2" t="inlineStr"/>
+      <c r="Z199" s="2" t="inlineStr"/>
+      <c r="AA199" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/pencho-dinev-95322961/</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t>Fib Trade Ltd</t>
+        </is>
+      </c>
+      <c r="B200" s="2" t="inlineStr">
+        <is>
+          <t>Fib Trade Ltd</t>
+        </is>
+      </c>
+      <c r="C200" s="2" t="inlineStr">
+        <is>
+          <t>31639</t>
+        </is>
+      </c>
+      <c r="D200" s="2" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="E200" s="2" t="inlineStr">
+        <is>
+          <t>Sofia</t>
+        </is>
+      </c>
+      <c r="F200" s="2" t="inlineStr">
+        <is>
+          <t>Sofia-City</t>
+        </is>
+      </c>
+      <c r="G200" s="2" t="inlineStr">
+        <is>
+          <t>10 ulitsa</t>
+        </is>
+      </c>
+      <c r="H200" s="2" t="inlineStr">
+        <is>
+          <t>1540</t>
+        </is>
+      </c>
+      <c r="I200" s="2" t="inlineStr">
+        <is>
+          <t>https://fibtrade.org</t>
+        </is>
+      </c>
+      <c r="J200" s="2" t="inlineStr"/>
+      <c r="K200" s="2" t="inlineStr"/>
+      <c r="L200" s="2" t="inlineStr"/>
+      <c r="M200" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N200" s="2" t="inlineStr">
+        <is>
+          <t>office@fibtrade.org</t>
+        </is>
+      </c>
+      <c r="O200" s="2" t="inlineStr">
+        <is>
+          <t>+359 2 973 8382</t>
+        </is>
+      </c>
+      <c r="P200" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q200" s="2" t="inlineStr"/>
+      <c r="R200" s="2" t="inlineStr"/>
+      <c r="S200" s="2" t="inlineStr"/>
+      <c r="T200" s="2" t="inlineStr"/>
+      <c r="U200" s="2" t="inlineStr"/>
+      <c r="V200" s="2" t="inlineStr"/>
+      <c r="W200" s="2" t="inlineStr">
+        <is>
+          <t>Rosen Gekov</t>
+        </is>
+      </c>
+      <c r="X200" s="2" t="inlineStr">
+        <is>
+          <t>Chief Executive Officer</t>
+        </is>
+      </c>
+      <c r="Y200" s="2" t="inlineStr"/>
+      <c r="Z200" s="2" t="inlineStr"/>
+      <c r="AA200" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/rosen-gekov-687696108/</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="inlineStr">
+        <is>
+          <t>Antastico Group Ood</t>
+        </is>
+      </c>
+      <c r="B201" s="2" t="inlineStr">
+        <is>
+          <t>Antastico Group Ood</t>
+        </is>
+      </c>
+      <c r="C201" s="2" t="inlineStr">
+        <is>
+          <t>34077</t>
+        </is>
+      </c>
+      <c r="D201" s="2" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="E201" s="2" t="inlineStr">
+        <is>
+          <t>Simeonovo</t>
+        </is>
+      </c>
+      <c r="F201" s="2" t="inlineStr">
+        <is>
+          <t>Yambol</t>
+        </is>
+      </c>
+      <c r="G201" s="2" t="inlineStr">
+        <is>
+          <t>Ul. Momina Salsa No.14a</t>
+        </is>
+      </c>
+      <c r="H201" s="2" t="inlineStr">
+        <is>
+          <t>1434</t>
+        </is>
+      </c>
+      <c r="I201" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fantastico.bg</t>
+        </is>
+      </c>
+      <c r="J201" s="2" t="inlineStr"/>
+      <c r="K201" s="2" t="inlineStr"/>
+      <c r="L201" s="2" t="inlineStr">
+        <is>
+          <t>3479</t>
+        </is>
+      </c>
+      <c r="M201" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N201" s="2" t="inlineStr">
+        <is>
+          <t>denica.dimitrova@fantastico.bg</t>
+        </is>
+      </c>
+      <c r="O201" s="2" t="inlineStr">
+        <is>
+          <t>+359 2 969 2500</t>
+        </is>
+      </c>
+      <c r="P201" s="2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="Q201" s="2" t="inlineStr">
+        <is>
+          <t>206255903</t>
+        </is>
+      </c>
+      <c r="R201" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/chain-stores-fantastico/</t>
+        </is>
+      </c>
+      <c r="S201" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/fantastico.stores/</t>
+        </is>
+      </c>
+      <c r="T201" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/fantasticostores</t>
+        </is>
+      </c>
+      <c r="U201" s="2" t="inlineStr"/>
+      <c r="V201" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCu7ZlcAyDfZ8QcGcP-9FVtw</t>
+        </is>
+      </c>
+      <c r="W201" s="2" t="inlineStr">
+        <is>
+          <t>Adrian Tsonev</t>
+        </is>
+      </c>
+      <c r="X201" s="2" t="inlineStr">
+        <is>
+          <t>Commercial Director</t>
+        </is>
+      </c>
+      <c r="Y201" s="2" t="inlineStr"/>
+      <c r="Z201" s="2" t="inlineStr"/>
+      <c r="AA201" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/adrian-tsonev-5020ab170/</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="inlineStr">
+        <is>
+          <t>Antastico Group Ood</t>
+        </is>
+      </c>
+      <c r="B202" s="2" t="inlineStr">
+        <is>
+          <t>Antastico Group Ood</t>
+        </is>
+      </c>
+      <c r="C202" s="2" t="inlineStr">
+        <is>
+          <t>34077</t>
+        </is>
+      </c>
+      <c r="D202" s="2" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="E202" s="2" t="inlineStr">
+        <is>
+          <t>Simeonovo</t>
+        </is>
+      </c>
+      <c r="F202" s="2" t="inlineStr">
+        <is>
+          <t>Yambol</t>
+        </is>
+      </c>
+      <c r="G202" s="2" t="inlineStr">
+        <is>
+          <t>Ul. Momina Salsa No.14a</t>
+        </is>
+      </c>
+      <c r="H202" s="2" t="inlineStr">
+        <is>
+          <t>1434</t>
+        </is>
+      </c>
+      <c r="I202" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fantastico.bg</t>
+        </is>
+      </c>
+      <c r="J202" s="2" t="inlineStr"/>
+      <c r="K202" s="2" t="inlineStr"/>
+      <c r="L202" s="2" t="inlineStr">
+        <is>
+          <t>3479</t>
+        </is>
+      </c>
+      <c r="M202" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N202" s="2" t="inlineStr">
+        <is>
+          <t>denica.dimitrova@fantastico.bg</t>
+        </is>
+      </c>
+      <c r="O202" s="2" t="inlineStr">
+        <is>
+          <t>+359 2 969 2500</t>
+        </is>
+      </c>
+      <c r="P202" s="2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="Q202" s="2" t="inlineStr">
+        <is>
+          <t>206255903</t>
+        </is>
+      </c>
+      <c r="R202" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/chain-stores-fantastico/</t>
+        </is>
+      </c>
+      <c r="S202" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/fantastico.stores/</t>
+        </is>
+      </c>
+      <c r="T202" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/fantasticostores</t>
+        </is>
+      </c>
+      <c r="U202" s="2" t="inlineStr"/>
+      <c r="V202" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCu7ZlcAyDfZ8QcGcP-9FVtw</t>
+        </is>
+      </c>
+      <c r="W202" s="2" t="inlineStr">
+        <is>
+          <t>Denica Dimitrova</t>
+        </is>
+      </c>
+      <c r="X202" s="2" t="inlineStr">
+        <is>
+          <t>Buyer</t>
+        </is>
+      </c>
+      <c r="Y202" s="2" t="inlineStr"/>
+      <c r="Z202" s="2" t="inlineStr"/>
+      <c r="AA202" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/denica-dimitrova-85a264113/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Bulgaria.xlsx
+++ b/BWI/bestwine_output/bestwine_Bulgaria.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA202"/>
+  <dimension ref="A1:AA213"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -21495,6 +21495,1133 @@
         </is>
       </c>
     </row>
+    <row r="203">
+      <c r="A203" s="2" t="inlineStr">
+        <is>
+          <t>Maxxium Bulgaria Eood</t>
+        </is>
+      </c>
+      <c r="B203" s="2" t="inlineStr">
+        <is>
+          <t>Maxxium Bulgaria Eood</t>
+        </is>
+      </c>
+      <c r="C203" s="2" t="inlineStr">
+        <is>
+          <t>22487</t>
+        </is>
+      </c>
+      <c r="D203" s="2" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="E203" s="2" t="inlineStr">
+        <is>
+          <t>Sofia</t>
+        </is>
+      </c>
+      <c r="F203" s="2" t="inlineStr">
+        <is>
+          <t>Sofia-City</t>
+        </is>
+      </c>
+      <c r="G203" s="2" t="inlineStr">
+        <is>
+          <t>40 Bulevard Bratya Buxton, Bakston</t>
+        </is>
+      </c>
+      <c r="H203" s="2" t="inlineStr">
+        <is>
+          <t>1618</t>
+        </is>
+      </c>
+      <c r="I203" s="2" t="inlineStr">
+        <is>
+          <t>https://maxxium.bg</t>
+        </is>
+      </c>
+      <c r="J203" s="2" t="inlineStr"/>
+      <c r="K203" s="2" t="inlineStr"/>
+      <c r="L203" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="M203" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N203" s="2" t="inlineStr">
+        <is>
+          <t>office@maxxium.bg</t>
+        </is>
+      </c>
+      <c r="O203" s="2" t="inlineStr">
+        <is>
+          <t>+359 2 956 6090</t>
+        </is>
+      </c>
+      <c r="P203" s="2" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="Q203" s="2" t="inlineStr">
+        <is>
+          <t>130591713</t>
+        </is>
+      </c>
+      <c r="R203" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/maxxium-bulgaria</t>
+        </is>
+      </c>
+      <c r="S203" s="2" t="inlineStr"/>
+      <c r="T203" s="2" t="inlineStr"/>
+      <c r="U203" s="2" t="inlineStr"/>
+      <c r="V203" s="2" t="inlineStr"/>
+      <c r="W203" s="2" t="inlineStr">
+        <is>
+          <t>Mary Hilal</t>
+        </is>
+      </c>
+      <c r="X203" s="2" t="inlineStr">
+        <is>
+          <t>Senior Brand Manager</t>
+        </is>
+      </c>
+      <c r="Y203" s="2" t="inlineStr"/>
+      <c r="Z203" s="2" t="inlineStr"/>
+      <c r="AA203" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/mary-hilal-b64634234/</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
+        <is>
+          <t>Maxxium Bulgaria Eood</t>
+        </is>
+      </c>
+      <c r="B204" s="2" t="inlineStr">
+        <is>
+          <t>Maxxium Bulgaria Eood</t>
+        </is>
+      </c>
+      <c r="C204" s="2" t="inlineStr">
+        <is>
+          <t>22487</t>
+        </is>
+      </c>
+      <c r="D204" s="2" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="E204" s="2" t="inlineStr">
+        <is>
+          <t>Sofia</t>
+        </is>
+      </c>
+      <c r="F204" s="2" t="inlineStr">
+        <is>
+          <t>Sofia-City</t>
+        </is>
+      </c>
+      <c r="G204" s="2" t="inlineStr">
+        <is>
+          <t>40 Bulevard Bratya Buxton, Bakston</t>
+        </is>
+      </c>
+      <c r="H204" s="2" t="inlineStr">
+        <is>
+          <t>1618</t>
+        </is>
+      </c>
+      <c r="I204" s="2" t="inlineStr">
+        <is>
+          <t>https://maxxium.bg</t>
+        </is>
+      </c>
+      <c r="J204" s="2" t="inlineStr"/>
+      <c r="K204" s="2" t="inlineStr"/>
+      <c r="L204" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="M204" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N204" s="2" t="inlineStr">
+        <is>
+          <t>office@maxxium.bg</t>
+        </is>
+      </c>
+      <c r="O204" s="2" t="inlineStr">
+        <is>
+          <t>+359 2 956 6090</t>
+        </is>
+      </c>
+      <c r="P204" s="2" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="Q204" s="2" t="inlineStr">
+        <is>
+          <t>130591713</t>
+        </is>
+      </c>
+      <c r="R204" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/maxxium-bulgaria</t>
+        </is>
+      </c>
+      <c r="S204" s="2" t="inlineStr"/>
+      <c r="T204" s="2" t="inlineStr"/>
+      <c r="U204" s="2" t="inlineStr"/>
+      <c r="V204" s="2" t="inlineStr"/>
+      <c r="W204" s="2" t="inlineStr">
+        <is>
+          <t>Ilian Spasov</t>
+        </is>
+      </c>
+      <c r="X204" s="2" t="inlineStr">
+        <is>
+          <t>Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y204" s="2" t="inlineStr"/>
+      <c r="Z204" s="2" t="inlineStr"/>
+      <c r="AA204" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ilian-spasov-12b72336/</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="inlineStr">
+        <is>
+          <t>Alves Ood</t>
+        </is>
+      </c>
+      <c r="B205" s="2" t="inlineStr">
+        <is>
+          <t>Alves Ood</t>
+        </is>
+      </c>
+      <c r="C205" s="2" t="inlineStr">
+        <is>
+          <t>24278</t>
+        </is>
+      </c>
+      <c r="D205" s="2" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="E205" s="2" t="inlineStr">
+        <is>
+          <t>Sozopol</t>
+        </is>
+      </c>
+      <c r="F205" s="2" t="inlineStr">
+        <is>
+          <t>Burgas</t>
+        </is>
+      </c>
+      <c r="G205" s="2" t="inlineStr">
+        <is>
+          <t>N13 N. Vaptsarov Street</t>
+        </is>
+      </c>
+      <c r="H205" s="2" t="inlineStr">
+        <is>
+          <t>8130</t>
+        </is>
+      </c>
+      <c r="I205" s="2" t="inlineStr">
+        <is>
+          <t>https://alves.bg</t>
+        </is>
+      </c>
+      <c r="J205" s="2" t="inlineStr"/>
+      <c r="K205" s="2" t="inlineStr"/>
+      <c r="L205" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="M205" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N205" s="2" t="inlineStr">
+        <is>
+          <t>alves_ltd@abv.bg</t>
+        </is>
+      </c>
+      <c r="O205" s="2" t="inlineStr">
+        <is>
+          <t>+359 55 023 311</t>
+        </is>
+      </c>
+      <c r="P205" s="2" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="Q205" s="2" t="inlineStr">
+        <is>
+          <t>102255036</t>
+        </is>
+      </c>
+      <c r="R205" s="2" t="inlineStr"/>
+      <c r="S205" s="2" t="inlineStr"/>
+      <c r="T205" s="2" t="inlineStr"/>
+      <c r="U205" s="2" t="inlineStr"/>
+      <c r="V205" s="2" t="inlineStr"/>
+      <c r="W205" s="2" t="inlineStr">
+        <is>
+          <t>Alexander Dimitrov</t>
+        </is>
+      </c>
+      <c r="X205" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y205" s="2" t="inlineStr"/>
+      <c r="Z205" s="2" t="inlineStr"/>
+      <c r="AA205" s="2" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="inlineStr">
+        <is>
+          <t>Alves Ood</t>
+        </is>
+      </c>
+      <c r="B206" s="2" t="inlineStr">
+        <is>
+          <t>Alves Ood</t>
+        </is>
+      </c>
+      <c r="C206" s="2" t="inlineStr">
+        <is>
+          <t>24278</t>
+        </is>
+      </c>
+      <c r="D206" s="2" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="E206" s="2" t="inlineStr">
+        <is>
+          <t>Sozopol</t>
+        </is>
+      </c>
+      <c r="F206" s="2" t="inlineStr">
+        <is>
+          <t>Burgas</t>
+        </is>
+      </c>
+      <c r="G206" s="2" t="inlineStr">
+        <is>
+          <t>N13 N. Vaptsarov Street</t>
+        </is>
+      </c>
+      <c r="H206" s="2" t="inlineStr">
+        <is>
+          <t>8130</t>
+        </is>
+      </c>
+      <c r="I206" s="2" t="inlineStr">
+        <is>
+          <t>https://alves.bg</t>
+        </is>
+      </c>
+      <c r="J206" s="2" t="inlineStr"/>
+      <c r="K206" s="2" t="inlineStr"/>
+      <c r="L206" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="M206" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N206" s="2" t="inlineStr">
+        <is>
+          <t>alves_ltd@abv.bg</t>
+        </is>
+      </c>
+      <c r="O206" s="2" t="inlineStr">
+        <is>
+          <t>+359 55 023 311</t>
+        </is>
+      </c>
+      <c r="P206" s="2" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="Q206" s="2" t="inlineStr">
+        <is>
+          <t>102255036</t>
+        </is>
+      </c>
+      <c r="R206" s="2" t="inlineStr"/>
+      <c r="S206" s="2" t="inlineStr"/>
+      <c r="T206" s="2" t="inlineStr"/>
+      <c r="U206" s="2" t="inlineStr"/>
+      <c r="V206" s="2" t="inlineStr"/>
+      <c r="W206" s="2" t="inlineStr">
+        <is>
+          <t>Ivaylo Georgiev</t>
+        </is>
+      </c>
+      <c r="X206" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y206" s="2" t="inlineStr"/>
+      <c r="Z206" s="2" t="inlineStr"/>
+      <c r="AA206" s="2" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="inlineStr">
+        <is>
+          <t>Best Wine Ltd.</t>
+        </is>
+      </c>
+      <c r="B207" s="2" t="inlineStr">
+        <is>
+          <t>Best Wine Ltd.</t>
+        </is>
+      </c>
+      <c r="C207" s="2" t="inlineStr">
+        <is>
+          <t>2207</t>
+        </is>
+      </c>
+      <c r="D207" s="2" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="E207" s="2" t="inlineStr">
+        <is>
+          <t>Sofia</t>
+        </is>
+      </c>
+      <c r="F207" s="2" t="inlineStr">
+        <is>
+          <t>Sofia-City</t>
+        </is>
+      </c>
+      <c r="G207" s="2" t="inlineStr">
+        <is>
+          <t>11 Ulitsa Andrey Germanov</t>
+        </is>
+      </c>
+      <c r="H207" s="2" t="inlineStr">
+        <is>
+          <t>1360</t>
+        </is>
+      </c>
+      <c r="I207" s="2" t="inlineStr">
+        <is>
+          <t>https://bestwine.bg</t>
+        </is>
+      </c>
+      <c r="J207" s="2" t="inlineStr"/>
+      <c r="K207" s="2" t="inlineStr"/>
+      <c r="L207" s="2" t="inlineStr"/>
+      <c r="M207" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N207" s="2" t="inlineStr">
+        <is>
+          <t>office@bestwine.bg</t>
+        </is>
+      </c>
+      <c r="O207" s="2" t="inlineStr"/>
+      <c r="P207" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q207" s="2" t="inlineStr"/>
+      <c r="R207" s="2" t="inlineStr"/>
+      <c r="S207" s="2" t="inlineStr"/>
+      <c r="T207" s="2" t="inlineStr"/>
+      <c r="U207" s="2" t="inlineStr"/>
+      <c r="V207" s="2" t="inlineStr"/>
+      <c r="W207" s="2" t="inlineStr">
+        <is>
+          <t>Dimitar (Hristov) Kuzmov</t>
+        </is>
+      </c>
+      <c r="X207" s="2" t="inlineStr">
+        <is>
+          <t>Sales And Marketing Manager</t>
+        </is>
+      </c>
+      <c r="Y207" s="2" t="inlineStr"/>
+      <c r="Z207" s="2" t="inlineStr"/>
+      <c r="AA207" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/dimitar-kuzmov-34a1538a/</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="inlineStr">
+        <is>
+          <t>Winebox Eood</t>
+        </is>
+      </c>
+      <c r="B208" s="2" t="inlineStr">
+        <is>
+          <t>Winebox Eood</t>
+        </is>
+      </c>
+      <c r="C208" s="2" t="inlineStr">
+        <is>
+          <t>2202</t>
+        </is>
+      </c>
+      <c r="D208" s="2" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="E208" s="2" t="inlineStr">
+        <is>
+          <t>Sofia</t>
+        </is>
+      </c>
+      <c r="F208" s="2" t="inlineStr">
+        <is>
+          <t>Sofia-City</t>
+        </is>
+      </c>
+      <c r="G208" s="2" t="inlineStr">
+        <is>
+          <t>33 Ulitsa Iskar</t>
+        </is>
+      </c>
+      <c r="H208" s="2" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="I208" s="2" t="inlineStr">
+        <is>
+          <t>https://www.winebox.bg</t>
+        </is>
+      </c>
+      <c r="J208" s="2" t="inlineStr"/>
+      <c r="K208" s="2" t="inlineStr"/>
+      <c r="L208" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M208" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N208" s="2" t="inlineStr">
+        <is>
+          <t>office@winebox.bg</t>
+        </is>
+      </c>
+      <c r="O208" s="2" t="inlineStr"/>
+      <c r="P208" s="2" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="Q208" s="2" t="inlineStr">
+        <is>
+          <t>175378641</t>
+        </is>
+      </c>
+      <c r="R208" s="2" t="inlineStr"/>
+      <c r="S208" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/WineboxLTD</t>
+        </is>
+      </c>
+      <c r="T208" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/winebox_ltd/</t>
+        </is>
+      </c>
+      <c r="U208" s="2" t="inlineStr"/>
+      <c r="V208" s="2" t="inlineStr"/>
+      <c r="W208" s="2" t="inlineStr">
+        <is>
+          <t>Svetla Karabadjakova</t>
+        </is>
+      </c>
+      <c r="X208" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y208" s="2" t="inlineStr"/>
+      <c r="Z208" s="2" t="inlineStr"/>
+      <c r="AA208" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/svetla-karabadjakova-0a160225</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="inlineStr">
+        <is>
+          <t>Winebox Eood</t>
+        </is>
+      </c>
+      <c r="B209" s="2" t="inlineStr">
+        <is>
+          <t>Winebox Eood</t>
+        </is>
+      </c>
+      <c r="C209" s="2" t="inlineStr">
+        <is>
+          <t>2202</t>
+        </is>
+      </c>
+      <c r="D209" s="2" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="E209" s="2" t="inlineStr">
+        <is>
+          <t>Sofia</t>
+        </is>
+      </c>
+      <c r="F209" s="2" t="inlineStr">
+        <is>
+          <t>Sofia-City</t>
+        </is>
+      </c>
+      <c r="G209" s="2" t="inlineStr">
+        <is>
+          <t>33 Ulitsa Iskar</t>
+        </is>
+      </c>
+      <c r="H209" s="2" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="I209" s="2" t="inlineStr">
+        <is>
+          <t>https://www.winebox.bg</t>
+        </is>
+      </c>
+      <c r="J209" s="2" t="inlineStr"/>
+      <c r="K209" s="2" t="inlineStr"/>
+      <c r="L209" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M209" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N209" s="2" t="inlineStr">
+        <is>
+          <t>office@winebox.bg</t>
+        </is>
+      </c>
+      <c r="O209" s="2" t="inlineStr"/>
+      <c r="P209" s="2" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="Q209" s="2" t="inlineStr">
+        <is>
+          <t>175378641</t>
+        </is>
+      </c>
+      <c r="R209" s="2" t="inlineStr"/>
+      <c r="S209" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/WineboxLTD</t>
+        </is>
+      </c>
+      <c r="T209" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/winebox_ltd/</t>
+        </is>
+      </c>
+      <c r="U209" s="2" t="inlineStr"/>
+      <c r="V209" s="2" t="inlineStr"/>
+      <c r="W209" s="2" t="inlineStr">
+        <is>
+          <t>Nikolay Dalakov</t>
+        </is>
+      </c>
+      <c r="X209" s="2" t="inlineStr">
+        <is>
+          <t>General Manager</t>
+        </is>
+      </c>
+      <c r="Y209" s="2" t="inlineStr"/>
+      <c r="Z209" s="2" t="inlineStr"/>
+      <c r="AA209" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/nikolay-dalakov-7118188a/</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="inlineStr">
+        <is>
+          <t>Drinklink.bg</t>
+        </is>
+      </c>
+      <c r="B210" s="2" t="inlineStr">
+        <is>
+          <t>Drinklink.bg</t>
+        </is>
+      </c>
+      <c r="C210" s="2" t="inlineStr">
+        <is>
+          <t>31640</t>
+        </is>
+      </c>
+      <c r="D210" s="2" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="E210" s="2" t="inlineStr">
+        <is>
+          <t>Sofia</t>
+        </is>
+      </c>
+      <c r="F210" s="2" t="inlineStr">
+        <is>
+          <t>Sofia-City</t>
+        </is>
+      </c>
+      <c r="G210" s="2" t="inlineStr">
+        <is>
+          <t>22 Ulitsa</t>
+        </is>
+      </c>
+      <c r="H210" s="2" t="inlineStr">
+        <is>
+          <t>1138</t>
+        </is>
+      </c>
+      <c r="I210" s="2" t="inlineStr">
+        <is>
+          <t>https://drinklink.bg</t>
+        </is>
+      </c>
+      <c r="J210" s="2" t="inlineStr"/>
+      <c r="K210" s="2" t="inlineStr"/>
+      <c r="L210" s="2" t="inlineStr"/>
+      <c r="M210" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N210" s="2" t="inlineStr">
+        <is>
+          <t>info@drinklink.bg</t>
+        </is>
+      </c>
+      <c r="O210" s="2" t="inlineStr"/>
+      <c r="P210" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q210" s="2" t="inlineStr"/>
+      <c r="R210" s="2" t="inlineStr"/>
+      <c r="S210" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/DrinkLinkbg-100157172487583/</t>
+        </is>
+      </c>
+      <c r="T210" s="2" t="inlineStr"/>
+      <c r="U210" s="2" t="inlineStr"/>
+      <c r="V210" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@drinklinkbg</t>
+        </is>
+      </c>
+      <c r="W210" s="2" t="inlineStr">
+        <is>
+          <t>Pencho Dinev</t>
+        </is>
+      </c>
+      <c r="X210" s="2" t="inlineStr">
+        <is>
+          <t>Marketing And Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y210" s="2" t="inlineStr"/>
+      <c r="Z210" s="2" t="inlineStr"/>
+      <c r="AA210" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/pencho-dinev-95322961/</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="inlineStr">
+        <is>
+          <t>Fib Trade Ltd</t>
+        </is>
+      </c>
+      <c r="B211" s="2" t="inlineStr">
+        <is>
+          <t>Fib Trade Ltd</t>
+        </is>
+      </c>
+      <c r="C211" s="2" t="inlineStr">
+        <is>
+          <t>31639</t>
+        </is>
+      </c>
+      <c r="D211" s="2" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="E211" s="2" t="inlineStr">
+        <is>
+          <t>Sofia</t>
+        </is>
+      </c>
+      <c r="F211" s="2" t="inlineStr">
+        <is>
+          <t>Sofia-City</t>
+        </is>
+      </c>
+      <c r="G211" s="2" t="inlineStr">
+        <is>
+          <t>10 ulitsa</t>
+        </is>
+      </c>
+      <c r="H211" s="2" t="inlineStr">
+        <is>
+          <t>1540</t>
+        </is>
+      </c>
+      <c r="I211" s="2" t="inlineStr">
+        <is>
+          <t>https://fibtrade.org</t>
+        </is>
+      </c>
+      <c r="J211" s="2" t="inlineStr"/>
+      <c r="K211" s="2" t="inlineStr"/>
+      <c r="L211" s="2" t="inlineStr"/>
+      <c r="M211" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N211" s="2" t="inlineStr">
+        <is>
+          <t>office@fibtrade.org</t>
+        </is>
+      </c>
+      <c r="O211" s="2" t="inlineStr">
+        <is>
+          <t>+359 2 973 8382</t>
+        </is>
+      </c>
+      <c r="P211" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q211" s="2" t="inlineStr"/>
+      <c r="R211" s="2" t="inlineStr"/>
+      <c r="S211" s="2" t="inlineStr"/>
+      <c r="T211" s="2" t="inlineStr"/>
+      <c r="U211" s="2" t="inlineStr"/>
+      <c r="V211" s="2" t="inlineStr"/>
+      <c r="W211" s="2" t="inlineStr">
+        <is>
+          <t>Rosen Gekov</t>
+        </is>
+      </c>
+      <c r="X211" s="2" t="inlineStr">
+        <is>
+          <t>Chief Executive Officer</t>
+        </is>
+      </c>
+      <c r="Y211" s="2" t="inlineStr"/>
+      <c r="Z211" s="2" t="inlineStr"/>
+      <c r="AA211" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/rosen-gekov-687696108/</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="inlineStr">
+        <is>
+          <t>Antastico Group Ood</t>
+        </is>
+      </c>
+      <c r="B212" s="2" t="inlineStr">
+        <is>
+          <t>Antastico Group Ood</t>
+        </is>
+      </c>
+      <c r="C212" s="2" t="inlineStr">
+        <is>
+          <t>34077</t>
+        </is>
+      </c>
+      <c r="D212" s="2" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="E212" s="2" t="inlineStr">
+        <is>
+          <t>Simeonovo</t>
+        </is>
+      </c>
+      <c r="F212" s="2" t="inlineStr">
+        <is>
+          <t>Yambol</t>
+        </is>
+      </c>
+      <c r="G212" s="2" t="inlineStr">
+        <is>
+          <t>Ul. Momina Salsa No.14a</t>
+        </is>
+      </c>
+      <c r="H212" s="2" t="inlineStr">
+        <is>
+          <t>1434</t>
+        </is>
+      </c>
+      <c r="I212" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fantastico.bg</t>
+        </is>
+      </c>
+      <c r="J212" s="2" t="inlineStr"/>
+      <c r="K212" s="2" t="inlineStr"/>
+      <c r="L212" s="2" t="inlineStr">
+        <is>
+          <t>3479</t>
+        </is>
+      </c>
+      <c r="M212" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N212" s="2" t="inlineStr">
+        <is>
+          <t>denica.dimitrova@fantastico.bg</t>
+        </is>
+      </c>
+      <c r="O212" s="2" t="inlineStr">
+        <is>
+          <t>+359 2 969 2500</t>
+        </is>
+      </c>
+      <c r="P212" s="2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="Q212" s="2" t="inlineStr">
+        <is>
+          <t>206255903</t>
+        </is>
+      </c>
+      <c r="R212" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/chain-stores-fantastico/</t>
+        </is>
+      </c>
+      <c r="S212" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/fantastico.stores/</t>
+        </is>
+      </c>
+      <c r="T212" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/fantasticostores</t>
+        </is>
+      </c>
+      <c r="U212" s="2" t="inlineStr"/>
+      <c r="V212" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCu7ZlcAyDfZ8QcGcP-9FVtw</t>
+        </is>
+      </c>
+      <c r="W212" s="2" t="inlineStr">
+        <is>
+          <t>Denica Dimitrova</t>
+        </is>
+      </c>
+      <c r="X212" s="2" t="inlineStr">
+        <is>
+          <t>Buyer</t>
+        </is>
+      </c>
+      <c r="Y212" s="2" t="inlineStr"/>
+      <c r="Z212" s="2" t="inlineStr"/>
+      <c r="AA212" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/denica-dimitrova-85a264113/</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="inlineStr">
+        <is>
+          <t>Antastico Group Ood</t>
+        </is>
+      </c>
+      <c r="B213" s="2" t="inlineStr">
+        <is>
+          <t>Antastico Group Ood</t>
+        </is>
+      </c>
+      <c r="C213" s="2" t="inlineStr">
+        <is>
+          <t>34077</t>
+        </is>
+      </c>
+      <c r="D213" s="2" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="E213" s="2" t="inlineStr">
+        <is>
+          <t>Simeonovo</t>
+        </is>
+      </c>
+      <c r="F213" s="2" t="inlineStr">
+        <is>
+          <t>Yambol</t>
+        </is>
+      </c>
+      <c r="G213" s="2" t="inlineStr">
+        <is>
+          <t>Ul. Momina Salsa No.14a</t>
+        </is>
+      </c>
+      <c r="H213" s="2" t="inlineStr">
+        <is>
+          <t>1434</t>
+        </is>
+      </c>
+      <c r="I213" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fantastico.bg</t>
+        </is>
+      </c>
+      <c r="J213" s="2" t="inlineStr"/>
+      <c r="K213" s="2" t="inlineStr"/>
+      <c r="L213" s="2" t="inlineStr">
+        <is>
+          <t>3479</t>
+        </is>
+      </c>
+      <c r="M213" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N213" s="2" t="inlineStr">
+        <is>
+          <t>denica.dimitrova@fantastico.bg</t>
+        </is>
+      </c>
+      <c r="O213" s="2" t="inlineStr">
+        <is>
+          <t>+359 2 969 2500</t>
+        </is>
+      </c>
+      <c r="P213" s="2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="Q213" s="2" t="inlineStr">
+        <is>
+          <t>206255903</t>
+        </is>
+      </c>
+      <c r="R213" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/chain-stores-fantastico/</t>
+        </is>
+      </c>
+      <c r="S213" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/fantastico.stores/</t>
+        </is>
+      </c>
+      <c r="T213" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/fantasticostores</t>
+        </is>
+      </c>
+      <c r="U213" s="2" t="inlineStr"/>
+      <c r="V213" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCu7ZlcAyDfZ8QcGcP-9FVtw</t>
+        </is>
+      </c>
+      <c r="W213" s="2" t="inlineStr">
+        <is>
+          <t>Adrian Tsonev</t>
+        </is>
+      </c>
+      <c r="X213" s="2" t="inlineStr">
+        <is>
+          <t>Commercial Director</t>
+        </is>
+      </c>
+      <c r="Y213" s="2" t="inlineStr"/>
+      <c r="Z213" s="2" t="inlineStr"/>
+      <c r="AA213" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/adrian-tsonev-5020ab170/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Bulgaria.xlsx
+++ b/BWI/bestwine_output/bestwine_Bulgaria.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA213"/>
+  <dimension ref="A1:AA216"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -22622,6 +22622,285 @@
         </is>
       </c>
     </row>
+    <row r="214">
+      <c r="A214" s="2" t="inlineStr">
+        <is>
+          <t>ONE GLASS A DAY EOOD</t>
+        </is>
+      </c>
+      <c r="B214" s="2" t="inlineStr"/>
+      <c r="C214" s="2" t="inlineStr">
+        <is>
+          <t>167826</t>
+        </is>
+      </c>
+      <c r="D214" s="2" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="E214" s="2" t="inlineStr">
+        <is>
+          <t>Sofia</t>
+        </is>
+      </c>
+      <c r="F214" s="2" t="inlineStr"/>
+      <c r="G214" s="2" t="inlineStr">
+        <is>
+          <t>Suhata Reka Distr., Bl. No No. 100, Entr. D, Fl. 1, Apt. 3</t>
+        </is>
+      </c>
+      <c r="H214" s="2" t="inlineStr">
+        <is>
+          <t>1517</t>
+        </is>
+      </c>
+      <c r="I214" s="2" t="inlineStr">
+        <is>
+          <t>https://oneglassaday.com</t>
+        </is>
+      </c>
+      <c r="J214" s="2" t="inlineStr"/>
+      <c r="K214" s="2" t="inlineStr"/>
+      <c r="L214" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M214" s="2" t="inlineStr">
+        <is>
+          <t>6488</t>
+        </is>
+      </c>
+      <c r="N214" s="2" t="inlineStr">
+        <is>
+          <t>01glassaday@gmail.com</t>
+        </is>
+      </c>
+      <c r="O214" s="2" t="inlineStr"/>
+      <c r="P214" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="Q214" s="2" t="inlineStr">
+        <is>
+          <t>207416619</t>
+        </is>
+      </c>
+      <c r="R214" s="2" t="inlineStr"/>
+      <c r="S214" s="2" t="inlineStr">
+        <is>
+          <t>https://m.facebook.com/100094133941181</t>
+        </is>
+      </c>
+      <c r="T214" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/one_glass_a_day/</t>
+        </is>
+      </c>
+      <c r="U214" s="2" t="inlineStr"/>
+      <c r="V214" s="2" t="inlineStr"/>
+      <c r="W214" s="2" t="inlineStr">
+        <is>
+          <t>ZOYA BURNAS</t>
+        </is>
+      </c>
+      <c r="X214" s="2" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="Y214" s="2" t="inlineStr"/>
+      <c r="Z214" s="2" t="inlineStr"/>
+      <c r="AA214" s="2" t="inlineStr"/>
+    </row>
+    <row r="215">
+      <c r="A215" s="2" t="inlineStr">
+        <is>
+          <t>Global Wines Ltd Eood</t>
+        </is>
+      </c>
+      <c r="B215" s="2" t="inlineStr">
+        <is>
+          <t>Global Wines Ltd Eood</t>
+        </is>
+      </c>
+      <c r="C215" s="2" t="inlineStr">
+        <is>
+          <t>91373</t>
+        </is>
+      </c>
+      <c r="D215" s="2" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="E215" s="2" t="inlineStr">
+        <is>
+          <t>Varna</t>
+        </is>
+      </c>
+      <c r="F215" s="2" t="inlineStr">
+        <is>
+          <t>Varna</t>
+        </is>
+      </c>
+      <c r="G215" s="2" t="inlineStr">
+        <is>
+          <t>281 Vladislav Varnenchik Blvd.</t>
+        </is>
+      </c>
+      <c r="H215" s="2" t="inlineStr">
+        <is>
+          <t>9009</t>
+        </is>
+      </c>
+      <c r="I215" s="2" t="inlineStr">
+        <is>
+          <t>https://globalwines.bg</t>
+        </is>
+      </c>
+      <c r="J215" s="2" t="inlineStr"/>
+      <c r="K215" s="2" t="inlineStr"/>
+      <c r="L215" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M215" s="2" t="inlineStr"/>
+      <c r="N215" s="2" t="inlineStr">
+        <is>
+          <t>office@globalwines.bg</t>
+        </is>
+      </c>
+      <c r="O215" s="2" t="inlineStr"/>
+      <c r="P215" s="2" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="Q215" s="2" t="inlineStr">
+        <is>
+          <t>203482461</t>
+        </is>
+      </c>
+      <c r="R215" s="2" t="inlineStr"/>
+      <c r="S215" s="2" t="inlineStr"/>
+      <c r="T215" s="2" t="inlineStr"/>
+      <c r="U215" s="2" t="inlineStr"/>
+      <c r="V215" s="2" t="inlineStr"/>
+      <c r="W215" s="2" t="inlineStr">
+        <is>
+          <t>Krasimira Kovacheva</t>
+        </is>
+      </c>
+      <c r="X215" s="2" t="inlineStr">
+        <is>
+          <t>Import Export Manager</t>
+        </is>
+      </c>
+      <c r="Y215" s="2" t="inlineStr"/>
+      <c r="Z215" s="2" t="inlineStr"/>
+      <c r="AA215" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/krasimira-kovacheva-a42513286/</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="inlineStr">
+        <is>
+          <t>Global Wines Ltd Eood</t>
+        </is>
+      </c>
+      <c r="B216" s="2" t="inlineStr">
+        <is>
+          <t>Global Wines Ltd Eood</t>
+        </is>
+      </c>
+      <c r="C216" s="2" t="inlineStr">
+        <is>
+          <t>91373</t>
+        </is>
+      </c>
+      <c r="D216" s="2" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="E216" s="2" t="inlineStr">
+        <is>
+          <t>Varna</t>
+        </is>
+      </c>
+      <c r="F216" s="2" t="inlineStr">
+        <is>
+          <t>Varna</t>
+        </is>
+      </c>
+      <c r="G216" s="2" t="inlineStr">
+        <is>
+          <t>281 Vladislav Varnenchik Blvd.</t>
+        </is>
+      </c>
+      <c r="H216" s="2" t="inlineStr">
+        <is>
+          <t>9009</t>
+        </is>
+      </c>
+      <c r="I216" s="2" t="inlineStr">
+        <is>
+          <t>https://globalwines.bg</t>
+        </is>
+      </c>
+      <c r="J216" s="2" t="inlineStr"/>
+      <c r="K216" s="2" t="inlineStr"/>
+      <c r="L216" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M216" s="2" t="inlineStr"/>
+      <c r="N216" s="2" t="inlineStr">
+        <is>
+          <t>office@globalwines.bg</t>
+        </is>
+      </c>
+      <c r="O216" s="2" t="inlineStr"/>
+      <c r="P216" s="2" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="Q216" s="2" t="inlineStr">
+        <is>
+          <t>203482461</t>
+        </is>
+      </c>
+      <c r="R216" s="2" t="inlineStr"/>
+      <c r="S216" s="2" t="inlineStr"/>
+      <c r="T216" s="2" t="inlineStr"/>
+      <c r="U216" s="2" t="inlineStr"/>
+      <c r="V216" s="2" t="inlineStr"/>
+      <c r="W216" s="2" t="inlineStr">
+        <is>
+          <t>Plamen Ivanovb</t>
+        </is>
+      </c>
+      <c r="X216" s="2" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="Y216" s="2" t="inlineStr"/>
+      <c r="Z216" s="2" t="inlineStr"/>
+      <c r="AA216" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/plamen-ivanov-3b497a1ab/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Bulgaria.xlsx
+++ b/BWI/bestwine_output/bestwine_Bulgaria.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA216"/>
+  <dimension ref="A1:AA217"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -22901,6 +22901,83 @@
         </is>
       </c>
     </row>
+    <row r="217">
+      <c r="A217" s="2" t="inlineStr">
+        <is>
+          <t>Vinomare Wine Store</t>
+        </is>
+      </c>
+      <c r="B217" s="2" t="inlineStr">
+        <is>
+          <t>Vinomare Wine Store</t>
+        </is>
+      </c>
+      <c r="C217" s="2" t="inlineStr">
+        <is>
+          <t>58313</t>
+        </is>
+      </c>
+      <c r="D217" s="2" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="E217" s="2" t="inlineStr">
+        <is>
+          <t>Burgas</t>
+        </is>
+      </c>
+      <c r="F217" s="2" t="inlineStr">
+        <is>
+          <t>Burgas</t>
+        </is>
+      </c>
+      <c r="G217" s="2" t="inlineStr">
+        <is>
+          <t>15 Ulitsa Sveti Nikola</t>
+        </is>
+      </c>
+      <c r="H217" s="2" t="inlineStr">
+        <is>
+          <t>8142</t>
+        </is>
+      </c>
+      <c r="I217" s="2" t="inlineStr">
+        <is>
+          <t>https://vinomare.me</t>
+        </is>
+      </c>
+      <c r="J217" s="2" t="inlineStr"/>
+      <c r="K217" s="2" t="inlineStr"/>
+      <c r="L217" s="2" t="inlineStr"/>
+      <c r="M217" s="2" t="inlineStr"/>
+      <c r="N217" s="2" t="inlineStr">
+        <is>
+          <t>info@vinomare.me</t>
+        </is>
+      </c>
+      <c r="O217" s="2" t="inlineStr"/>
+      <c r="P217" s="2" t="inlineStr"/>
+      <c r="Q217" s="2" t="inlineStr"/>
+      <c r="R217" s="2" t="inlineStr"/>
+      <c r="S217" s="2" t="inlineStr"/>
+      <c r="T217" s="2" t="inlineStr"/>
+      <c r="U217" s="2" t="inlineStr"/>
+      <c r="V217" s="2" t="inlineStr"/>
+      <c r="W217" s="2" t="inlineStr">
+        <is>
+          <t>Georgi Georgievi</t>
+        </is>
+      </c>
+      <c r="X217" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y217" s="2" t="inlineStr"/>
+      <c r="Z217" s="2" t="inlineStr"/>
+      <c r="AA217" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Bulgaria.xlsx
+++ b/BWI/bestwine_output/bestwine_Bulgaria.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA217"/>
+  <dimension ref="A1:AA219"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -22978,6 +22978,200 @@
       <c r="Z217" s="2" t="inlineStr"/>
       <c r="AA217" s="2" t="inlineStr"/>
     </row>
+    <row r="218">
+      <c r="A218" s="2" t="inlineStr">
+        <is>
+          <t>Casavino Wine Shop</t>
+        </is>
+      </c>
+      <c r="B218" s="2" t="inlineStr">
+        <is>
+          <t>Casavino Wine Shop</t>
+        </is>
+      </c>
+      <c r="C218" s="2" t="inlineStr">
+        <is>
+          <t>31490</t>
+        </is>
+      </c>
+      <c r="D218" s="2" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="E218" s="2" t="inlineStr">
+        <is>
+          <t>Sofia</t>
+        </is>
+      </c>
+      <c r="F218" s="2" t="inlineStr">
+        <is>
+          <t>Sofia-City</t>
+        </is>
+      </c>
+      <c r="G218" s="2" t="inlineStr">
+        <is>
+          <t>14 Ulitsa Antim I Sofia Center</t>
+        </is>
+      </c>
+      <c r="H218" s="2" t="inlineStr">
+        <is>
+          <t>1303</t>
+        </is>
+      </c>
+      <c r="I218" s="2" t="inlineStr">
+        <is>
+          <t>https://casavino.bg</t>
+        </is>
+      </c>
+      <c r="J218" s="2" t="inlineStr"/>
+      <c r="K218" s="2" t="inlineStr"/>
+      <c r="L218" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="M218" s="2" t="inlineStr"/>
+      <c r="N218" s="2" t="inlineStr">
+        <is>
+          <t>vinoto@casavino.bg</t>
+        </is>
+      </c>
+      <c r="O218" s="2" t="inlineStr"/>
+      <c r="P218" s="2" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="Q218" s="2" t="inlineStr">
+        <is>
+          <t>200242774</t>
+        </is>
+      </c>
+      <c r="R218" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/vino-distributsia-eood/</t>
+        </is>
+      </c>
+      <c r="S218" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/casavinowineshop/</t>
+        </is>
+      </c>
+      <c r="T218" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/casavino_wine_shop</t>
+        </is>
+      </c>
+      <c r="U218" s="2" t="inlineStr"/>
+      <c r="V218" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@casavinowineshop6192</t>
+        </is>
+      </c>
+      <c r="W218" s="2" t="inlineStr">
+        <is>
+          <t>Stanislav Velikov</t>
+        </is>
+      </c>
+      <c r="X218" s="2" t="inlineStr">
+        <is>
+          <t>Wine Stores Manager</t>
+        </is>
+      </c>
+      <c r="Y218" s="2" t="inlineStr"/>
+      <c r="Z218" s="2" t="inlineStr"/>
+      <c r="AA218" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/stanislav-velikov-39781930</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="2" t="inlineStr">
+        <is>
+          <t>Jodi Trade Ood</t>
+        </is>
+      </c>
+      <c r="B219" s="2" t="inlineStr">
+        <is>
+          <t>Jodi Trade Ood</t>
+        </is>
+      </c>
+      <c r="C219" s="2" t="inlineStr">
+        <is>
+          <t>58269</t>
+        </is>
+      </c>
+      <c r="D219" s="2" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="E219" s="2" t="inlineStr">
+        <is>
+          <t>Sofia</t>
+        </is>
+      </c>
+      <c r="F219" s="2" t="inlineStr">
+        <is>
+          <t>Sofia-City</t>
+        </is>
+      </c>
+      <c r="G219" s="2" t="inlineStr">
+        <is>
+          <t>25 Ulitsa</t>
+        </is>
+      </c>
+      <c r="H219" s="2" t="inlineStr">
+        <is>
+          <t>1172</t>
+        </is>
+      </c>
+      <c r="I219" s="2" t="inlineStr">
+        <is>
+          <t>https://enjoywine.bg</t>
+        </is>
+      </c>
+      <c r="J219" s="2" t="inlineStr"/>
+      <c r="K219" s="2" t="inlineStr"/>
+      <c r="L219" s="2" t="inlineStr"/>
+      <c r="M219" s="2" t="inlineStr"/>
+      <c r="N219" s="2" t="inlineStr">
+        <is>
+          <t>office@enjoywine.bg</t>
+        </is>
+      </c>
+      <c r="O219" s="2" t="inlineStr"/>
+      <c r="P219" s="2" t="inlineStr"/>
+      <c r="Q219" s="2" t="inlineStr"/>
+      <c r="R219" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/enjoywine/</t>
+        </is>
+      </c>
+      <c r="S219" s="2" t="inlineStr"/>
+      <c r="T219" s="2" t="inlineStr"/>
+      <c r="U219" s="2" t="inlineStr"/>
+      <c r="V219" s="2" t="inlineStr"/>
+      <c r="W219" s="2" t="inlineStr">
+        <is>
+          <t>Evelina Dimitrova</t>
+        </is>
+      </c>
+      <c r="X219" s="2" t="inlineStr">
+        <is>
+          <t>Ceo</t>
+        </is>
+      </c>
+      <c r="Y219" s="2" t="inlineStr"/>
+      <c r="Z219" s="2" t="inlineStr"/>
+      <c r="AA219" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/evelina-dimitrova-79ba68102/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
